--- a/AUTOTESTJSON/TemplateReport.xlsx
+++ b/AUTOTESTJSON/TemplateReport.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="28800" windowHeight="13980"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="20">
   <si>
     <t>STT</t>
   </si>
@@ -89,28 +89,6 @@
   </si>
   <si>
     <t>Pass</t>
-  </si>
-  <si>
-    <t>仕口の絞りに制限をかけたいです。</t>
-  </si>
-  <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>仕口絞り制限の設定を行いたいです。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2/Làm sao để setting độ dày giới hạn cho tấm diagram bên trong </t>
-  </si>
-  <si>
-    <t>2/内ダイア厚さを制限したいです。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1/Dẫn đến file 内ダイア厚さの制限㎜: https://drive.google.com/drive/folders/1VgFcYNgTQk-f9-spOHEVWmVM85nNkMPB
- </t>
-  </si>
-  <si>
-    <t>内ダイアの厚さに制限をかけたいです。</t>
   </si>
 </sst>
 </file>
@@ -1059,8 +1037,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P7"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6"/>
+  <dimension ref="A1:P3"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="2"/>
+  <cols>
+    <col min="5" max="5" width="14.1428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:12">
       <c r="A1">
@@ -1180,92 +1161,6 @@
       </c>
       <c r="L3" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="4" ht="345" spans="1:16">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" t="s">
-        <v>19</v>
-      </c>
-      <c r="P4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" ht="345" spans="1:12">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" ht="265.5" spans="1:12">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-      <c r="I6" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" t="s">
-        <v>19</v>
-      </c>
-      <c r="K6" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" ht="265.5" spans="1:16">
-      <c r="A7">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="L7" t="s">
-        <v>19</v>
-      </c>
-      <c r="P7" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
